--- a/v3/OG0049/OG0049_ReadingQuiz.xlsx
+++ b/v3/OG0049/OG0049_ReadingQuiz.xlsx
@@ -840,12 +840,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>What is Toby thinking?</t>
+          <t>What is Kira thinking?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Think about what Toby wants to do now.</t>
+          <t>Think about what Kira learns about trash.</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
@@ -1884,17 +1884,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>SC03</t>
+          <t>SC04</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>OG0049_SC03_I.webp</t>
+          <t>OG0049_SC04_I.webp</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>SC03</t>
+          <t>SC04</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>kira_toby</t>
+          <t>aurora_submarine</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>deep_ocean</t>
+          <t>dark_canyon</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>see_light</t>
+          <t>followed_light</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>kira_toby</t>
+          <t>aurora_submarine</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>deep_ocean</t>
+          <t>dark_canyon</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>see_light</t>
+          <t>followed_light</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -2231,7 +2231,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Kira and Toby</t>
+          <t>the Aurora submarine</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>deep in the ocean</t>
+          <t>into the dark canyon</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>see a tiny golden light</t>
+          <t>followed the light</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3179,7 +3179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>["arms.", "robot", "silver", "submarine's", "the", "opened", "Toby", "Diver"]</t>
+          <t>["arms.", "robot", "silver", "the submarine's", "opened", "Toby", "Diver"]</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>["Diver", "Toby", "opened", "the", "submarine's", "silver", "robot", "arms."]</t>
+          <t>["Diver", "Toby", "opened", "the submarine's", "silver", "robot", "arms."]</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr"/>
@@ -3535,7 +3535,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>the</t>
+          <t>the submarine's</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
@@ -3561,7 +3561,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>submarine's</t>
+          <t>silver</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
@@ -3587,7 +3587,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>silver</t>
+          <t>robot</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
@@ -3613,11 +3613,11 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>robot</t>
+          <t>arms.</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
@@ -3637,90 +3637,64 @@
       <c r="H17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>arms.</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>exact_position</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Actor/action/result word order.</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SECTION D</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>SECTION D</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Diagnostics</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Threshold</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>attempt_sentence_gap</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B20" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>인물이 문제를 해결하려고 한 행동 문장을 순서대로 구성하는 연습이 필요합니다.</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4346,7 +4320,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>What is Toby thinking?</t>
+          <t>What is Kira thinking?</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -4356,7 +4330,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Think about what Toby wants to do now.</t>
+          <t>Think about what Kira learns about trash.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -4462,17 +4436,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>SC09</t>
+          <t>SC15</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>OG0049_SC09_I.webp</t>
+          <t>OG0049_SC15_I.webp</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>SC09</t>
+          <t>SC15</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
@@ -4536,7 +4510,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>We must act now!</t>
+          <t>We should keep the ocean clean.</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
@@ -4560,7 +4534,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>The light is not important.</t>
+          <t>Plastic bags are not dangerous.</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
@@ -4573,7 +4547,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>중심 문제를 놓치고 반대되는 생각을 선택합니다.</t>
+          <t>이야기의 핵심 깨달음과 반대되는 생각을 선택합니다.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr"/>
@@ -4588,11 +4562,11 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>The fish can fix it alone.</t>
+          <t>One fish is not important.</t>
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
@@ -4601,7 +4575,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>도움이 필요한 상황과 인물의 의도를 연결하지 못합니다.</t>
+          <t>인물의 책임감과 생명 보호 의도를 약하게 이해함</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr"/>
@@ -4609,27 +4583,27 @@
       <c r="H11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>The cave is beautiful.</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>We should leave the trash in the sea.</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>위험 단서를 배경 묘사로만 이해함</t>
+          <t>환경 보호 메시지와 반대되는 생각을 선택합니다.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr"/>
@@ -4734,7 +4708,7 @@
       <c r="E16" s="3" t="inlineStr"/>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>중심 문제를 놓치고 반대되는 생각을 선택합니다.</t>
+          <t>이야기의 핵심 깨달음과 반대되는 생각을 선택합니다.</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -4747,7 +4721,7 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
@@ -4760,7 +4734,7 @@
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>도움이 필요한 상황과 인물의 의도를 연결하지 못합니다.</t>
+          <t>인물의 책임감과 생명 보호 의도를 약하게 이해함</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -4772,8 +4746,8 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
-        <v>10</v>
+      <c r="B18" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
@@ -4786,7 +4760,7 @@
       <c r="E18" s="3" t="inlineStr"/>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>위험 단서를 배경 묘사로만 이해함</t>
+          <t>환경 보호 메시지와 반대되는 생각을 선택합니다.</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
